--- a/field/hanoi_noise_form.xlsx
+++ b/field/hanoi_noise_form.xlsx
@@ -483,12 +483,6 @@
           <t>start_time</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -501,12 +495,6 @@
           <t>end_time</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -529,9 +517,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>minimal</t>
@@ -559,9 +544,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>minimal</t>
@@ -589,14 +571,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Stand still a few seconds for better accuracy</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -619,14 +598,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Record at least 10 s of ambient sound</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -664,7 +640,6 @@
           <t>Read LAeq / average value from the dB app</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -687,8 +662,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Dominant sound source</t>
@@ -721,9 +694,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>minimal</t>
@@ -746,15 +716,11 @@
           <t>Note (optional)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Unusual events: horn burst, rain, festival...</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -767,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,12 +829,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>collector_1</t>
+          <t>laurian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Collector 1</t>
+          <t>Laurian</t>
         </is>
       </c>
     </row>
@@ -880,29 +846,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>collector_2</t>
+          <t>lucas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Collector 2</t>
+          <t>Lucas</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>collector</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>xe_may_motorbike</t>
+          <t>quang</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Motorbike (xe may)</t>
+          <t>Quang</t>
         </is>
       </c>
     </row>
@@ -914,12 +880,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>car_or_truck</t>
+          <t>xe_may_motorbike</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Car or truck</t>
+          <t>Motorbike (xe may)</t>
         </is>
       </c>
     </row>
@@ -931,12 +897,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>motor_vehicle_horn</t>
+          <t>car_or_truck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vehicle horn / honking</t>
+          <t>Car or truck</t>
         </is>
       </c>
     </row>
@@ -948,12 +914,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>construction_site</t>
+          <t>motor_vehicle_horn</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Construction site (drilling, hammering...)</t>
+          <t>Vehicle horn / honking</t>
         </is>
       </c>
     </row>
@@ -965,12 +931,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>street_vendor</t>
+          <t>construction_site</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Street vendor / hawker</t>
+          <t>Construction site (drilling, hammering...)</t>
         </is>
       </c>
     </row>
@@ -982,12 +948,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>karaoke_restaurant</t>
+          <t>street_vendor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Karaoke / restaurant / bar</t>
+          <t>Street vendor / hawker</t>
         </is>
       </c>
     </row>
@@ -999,12 +965,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>crowd_noise</t>
+          <t>karaoke_restaurant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Crowd noise</t>
+          <t>Karaoke / restaurant / bar</t>
         </is>
       </c>
     </row>
@@ -1016,12 +982,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>crowd_noise</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Crowd noise</t>
         </is>
       </c>
     </row>
@@ -1033,12 +999,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>animal</t>
+          <t>school</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Animal</t>
+          <t>School</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1016,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>silence</t>
+          <t>animal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Silence / quiet ambient</t>
+          <t>Animal</t>
         </is>
       </c>
     </row>
@@ -1067,29 +1033,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>silence</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Silence / quiet ambient</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dist</t>
+          <t>category</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>d_0_10</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0-10 m</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1067,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>d_10_30</t>
+          <t>d_0_10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10-30 m</t>
+          <t>0-10 m</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1084,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>d_30_60</t>
+          <t>d_10_30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>30-60 m</t>
+          <t>10-30 m</t>
         </is>
       </c>
     </row>
@@ -1135,10 +1101,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>d_30_60</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>30-60 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>dist</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>d_60plus</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>&gt; 60 m / behind building</t>
         </is>
@@ -1188,7 +1171,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026061001</t>
+          <t>2026061002</t>
         </is>
       </c>
     </row>
